--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/99.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/99.xlsx
@@ -426,13 +426,13 @@
         <v>-24.22621771757034</v>
       </c>
       <c r="E2">
-        <v>-23.99915158076366</v>
+        <v>-18.59781718859764</v>
       </c>
       <c r="F2">
-        <v>-5.813185196196833</v>
+        <v>-4.2536758726644</v>
       </c>
       <c r="G2">
-        <v>-15.79514521227422</v>
+        <v>-10.94363639440497</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.80179681811121</v>
       </c>
       <c r="E3">
-        <v>-24.78030833279403</v>
+        <v>-18.65712089310487</v>
       </c>
       <c r="F3">
-        <v>-5.848080173039762</v>
+        <v>-4.287368888405867</v>
       </c>
       <c r="G3">
-        <v>-13.94503453092031</v>
+        <v>-10.70988990430112</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-23.34443541591304</v>
       </c>
       <c r="E4">
-        <v>-25.74905733394426</v>
+        <v>-18.64277985440023</v>
       </c>
       <c r="F4">
-        <v>-5.819390496411204</v>
+        <v>-4.309617180110256</v>
       </c>
       <c r="G4">
-        <v>-14.16348597383712</v>
+        <v>-10.41822404544342</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.92298354661438</v>
       </c>
       <c r="E5">
-        <v>-26.49026849945244</v>
+        <v>-19.57341898843384</v>
       </c>
       <c r="F5">
-        <v>-5.400883545536241</v>
+        <v>-4.441683795138581</v>
       </c>
       <c r="G5">
-        <v>-13.90014408304841</v>
+        <v>-10.38348939403095</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.52600143060464</v>
       </c>
       <c r="E6">
-        <v>-28.14186358736303</v>
+        <v>-19.43260435846553</v>
       </c>
       <c r="F6">
-        <v>-5.173670650622364</v>
+        <v>-4.65362325187964</v>
       </c>
       <c r="G6">
-        <v>-13.86022449287799</v>
+        <v>-10.02357083932778</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.16676809734852</v>
       </c>
       <c r="E7">
-        <v>-26.33081010384698</v>
+        <v>-20.12644399560271</v>
       </c>
       <c r="F7">
-        <v>-5.220108927223305</v>
+        <v>-4.245651477633481</v>
       </c>
       <c r="G7">
-        <v>-13.82771419585715</v>
+        <v>-9.586256761221053</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.84339982694776</v>
       </c>
       <c r="E8">
-        <v>-27.00147066858029</v>
+        <v>-21.09833697772584</v>
       </c>
       <c r="F8">
-        <v>-5.539982171446931</v>
+        <v>-4.001655030771484</v>
       </c>
       <c r="G8">
-        <v>-14.33404722334685</v>
+        <v>-9.423459866125297</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.54698609341519</v>
       </c>
       <c r="E9">
-        <v>-26.96015867553222</v>
+        <v>-21.65578930816697</v>
       </c>
       <c r="F9">
-        <v>-4.78741038600358</v>
+        <v>-4.150670042861087</v>
       </c>
       <c r="G9">
-        <v>-13.95168931888306</v>
+        <v>-8.420713335219848</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.27855756457659</v>
       </c>
       <c r="E10">
-        <v>-27.88720943498117</v>
+        <v>-22.89452611791033</v>
       </c>
       <c r="F10">
-        <v>-5.623059138273693</v>
+        <v>-3.739644078000806</v>
       </c>
       <c r="G10">
-        <v>-13.37875228075718</v>
+        <v>-9.115602169313515</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.02532406525773</v>
       </c>
       <c r="E11">
-        <v>-29.06382458633341</v>
+        <v>-23.06794760998988</v>
       </c>
       <c r="F11">
-        <v>-5.373025549780094</v>
+        <v>-3.899697914100115</v>
       </c>
       <c r="G11">
-        <v>-12.88724436642812</v>
+        <v>-8.144140190843375</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.79249756334999</v>
       </c>
       <c r="E12">
-        <v>-28.62763356694329</v>
+        <v>-23.93691155584978</v>
       </c>
       <c r="F12">
-        <v>-5.489410341506021</v>
+        <v>-3.662264622170499</v>
       </c>
       <c r="G12">
-        <v>-13.24931156392978</v>
+        <v>-7.543232940540602</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.56802524070177</v>
       </c>
       <c r="E13">
-        <v>-29.05633634631474</v>
+        <v>-24.1294835053481</v>
       </c>
       <c r="F13">
-        <v>-5.343859561894925</v>
+        <v>-3.802500596525233</v>
       </c>
       <c r="G13">
-        <v>-12.14473163487566</v>
+        <v>-7.647234562072192</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-20.34980038958531</v>
       </c>
       <c r="E14">
-        <v>-30.41068194649603</v>
+        <v>-25.71410390743451</v>
       </c>
       <c r="F14">
-        <v>-4.833511517071581</v>
+        <v>-3.462676951772583</v>
       </c>
       <c r="G14">
-        <v>-12.78227154790864</v>
+        <v>-7.302595390088509</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-20.13153926982645</v>
       </c>
       <c r="E15">
-        <v>-32.41013547873462</v>
+        <v>-25.41793425464966</v>
       </c>
       <c r="F15">
-        <v>-4.561574237713157</v>
+        <v>-3.39698990183279</v>
       </c>
       <c r="G15">
-        <v>-12.31792712567782</v>
+        <v>-7.691178615029811</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.89570345127758</v>
       </c>
       <c r="E16">
-        <v>-31.50049082794803</v>
+        <v>-26.58064653109204</v>
       </c>
       <c r="F16">
-        <v>-4.525518718138906</v>
+        <v>-3.087999748547144</v>
       </c>
       <c r="G16">
-        <v>-11.71507095453778</v>
+        <v>-6.654694737145698</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.63998776902262</v>
       </c>
       <c r="E17">
-        <v>-32.45274742692737</v>
+        <v>-27.23518432946236</v>
       </c>
       <c r="F17">
-        <v>-4.477813039411681</v>
+        <v>-3.196150568289245</v>
       </c>
       <c r="G17">
-        <v>-12.57364433688818</v>
+        <v>-6.657365528862408</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-19.35052081992441</v>
       </c>
       <c r="E18">
-        <v>-32.38978474324296</v>
+        <v>-27.15066232579078</v>
       </c>
       <c r="F18">
-        <v>-4.837580457754132</v>
+        <v>-3.012795585516588</v>
       </c>
       <c r="G18">
-        <v>-11.78704526679789</v>
+        <v>-6.724485161555338</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.0361683708667</v>
       </c>
       <c r="E19">
-        <v>-32.55571799530384</v>
+        <v>-28.27086648432353</v>
       </c>
       <c r="F19">
-        <v>-4.574606113693998</v>
+        <v>-2.578982061772695</v>
       </c>
       <c r="G19">
-        <v>-11.48211552004504</v>
+        <v>-6.534759741374545</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.69686144470658</v>
       </c>
       <c r="E20">
-        <v>-33.7296854744365</v>
+        <v>-29.00352618771388</v>
       </c>
       <c r="F20">
-        <v>-4.08423000695215</v>
+        <v>-2.45660900209193</v>
       </c>
       <c r="G20">
-        <v>-11.23305309679742</v>
+        <v>-6.599587140316479</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.34107795650567</v>
       </c>
       <c r="E21">
-        <v>-34.00697878175</v>
+        <v>-29.51966444850129</v>
       </c>
       <c r="F21">
-        <v>-3.21660461619917</v>
+        <v>-2.311893216822857</v>
       </c>
       <c r="G21">
-        <v>-10.61721108206119</v>
+        <v>-6.647329826654167</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.97666148683643</v>
       </c>
       <c r="E22">
-        <v>-33.51968872682485</v>
+        <v>-29.6202074648584</v>
       </c>
       <c r="F22">
-        <v>-3.576631313538697</v>
+        <v>-1.740599697073344</v>
       </c>
       <c r="G22">
-        <v>-11.4954942807022</v>
+        <v>-6.802011222188447</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.60137979213224</v>
       </c>
       <c r="E23">
-        <v>-36.19671376744127</v>
+        <v>-30.40136006367745</v>
       </c>
       <c r="F23">
-        <v>-3.996900201879415</v>
+        <v>-1.617636011434382</v>
       </c>
       <c r="G23">
-        <v>-11.20950679133017</v>
+        <v>-6.933441326394273</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.22872582287729</v>
       </c>
       <c r="E24">
-        <v>-35.30823803477733</v>
+        <v>-29.94032453414221</v>
       </c>
       <c r="F24">
-        <v>-3.286428532948543</v>
+        <v>-1.841642296132022</v>
       </c>
       <c r="G24">
-        <v>-11.05496245988693</v>
+        <v>-7.362637294194933</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.86038705235162</v>
       </c>
       <c r="E25">
-        <v>-34.98003673964974</v>
+        <v>-29.68244956637794</v>
       </c>
       <c r="F25">
-        <v>-3.272729821208448</v>
+        <v>-1.633606106592954</v>
       </c>
       <c r="G25">
-        <v>-11.69807239650504</v>
+        <v>-7.904668337851213</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.51425156152207</v>
       </c>
       <c r="E26">
-        <v>-34.37212496821761</v>
+        <v>-31.19567003597356</v>
       </c>
       <c r="F26">
-        <v>-3.508228875252528</v>
+        <v>-1.835991173710124</v>
       </c>
       <c r="G26">
-        <v>-11.84902564876321</v>
+        <v>-7.329914221489918</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.20173726061389</v>
       </c>
       <c r="E27">
-        <v>-35.31151907172394</v>
+        <v>-30.5242494335678</v>
       </c>
       <c r="F27">
-        <v>-3.151452691601586</v>
+        <v>-1.470426840282882</v>
       </c>
       <c r="G27">
-        <v>-11.55773573712664</v>
+        <v>-7.479408067521656</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.93655973416708</v>
       </c>
       <c r="E28">
-        <v>-35.02306400897496</v>
+        <v>-29.96791016376172</v>
       </c>
       <c r="F28">
-        <v>-3.821643338836526</v>
+        <v>-1.807122569722561</v>
       </c>
       <c r="G28">
-        <v>-11.09645893979038</v>
+        <v>-7.774517498495033</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.73595038227735</v>
       </c>
       <c r="E29">
-        <v>-35.33469399091649</v>
+        <v>-30.28947462719223</v>
       </c>
       <c r="F29">
-        <v>-2.947447337844541</v>
+        <v>-1.72412015596205</v>
       </c>
       <c r="G29">
-        <v>-11.60311439423707</v>
+        <v>-8.609861780846005</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.60213527485103</v>
       </c>
       <c r="E30">
-        <v>-34.84631994783556</v>
+        <v>-31.01510294380965</v>
       </c>
       <c r="F30">
-        <v>-3.410426021106198</v>
+        <v>-1.350721123639131</v>
       </c>
       <c r="G30">
-        <v>-12.1501841749542</v>
+        <v>-8.28645448924955</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.54697978071622</v>
       </c>
       <c r="E31">
-        <v>-34.79570060820856</v>
+        <v>-30.12665628362498</v>
       </c>
       <c r="F31">
-        <v>-3.493428434866709</v>
+        <v>-1.54240037044252</v>
       </c>
       <c r="G31">
-        <v>-11.50852059083956</v>
+        <v>-8.68520917511783</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.56321301370057</v>
       </c>
       <c r="E32">
-        <v>-33.62075712441456</v>
+        <v>-29.18321279907693</v>
       </c>
       <c r="F32">
-        <v>-3.395891486656678</v>
+        <v>-1.291755446805654</v>
       </c>
       <c r="G32">
-        <v>-12.75420995967106</v>
+        <v>-8.610173764824642</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.64628864546224</v>
       </c>
       <c r="E33">
-        <v>-33.65516855684643</v>
+        <v>-28.89451062025412</v>
       </c>
       <c r="F33">
-        <v>-2.549820215724542</v>
+        <v>-1.218620545547291</v>
       </c>
       <c r="G33">
-        <v>-11.5144443703168</v>
+        <v>-9.027852432861605</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.7866280593439</v>
       </c>
       <c r="E34">
-        <v>-33.49234190685652</v>
+        <v>-28.84089473865625</v>
       </c>
       <c r="F34">
-        <v>-2.494282323203849</v>
+        <v>-1.095192974162762</v>
       </c>
       <c r="G34">
-        <v>-12.12294627663512</v>
+        <v>-8.765232412952338</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.96774268654569</v>
       </c>
       <c r="E35">
-        <v>-33.56840174245377</v>
+        <v>-28.07919370507703</v>
       </c>
       <c r="F35">
-        <v>-3.142494726507712</v>
+        <v>-1.206616673513324</v>
       </c>
       <c r="G35">
-        <v>-13.1793579679832</v>
+        <v>-9.367572962035631</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.18392225698653</v>
       </c>
       <c r="E36">
-        <v>-32.78662616193599</v>
+        <v>-28.11297177278186</v>
       </c>
       <c r="F36">
-        <v>-3.197715354313133</v>
+        <v>-0.7271253144442605</v>
       </c>
       <c r="G36">
-        <v>-11.53959497833529</v>
+        <v>-9.277681109646714</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-16.41744346430002</v>
       </c>
       <c r="E37">
-        <v>-33.89060787703396</v>
+        <v>-27.24948798926507</v>
       </c>
       <c r="F37">
-        <v>-3.034184860224274</v>
+        <v>-0.8642897024694139</v>
       </c>
       <c r="G37">
-        <v>-12.86163948885078</v>
+        <v>-9.598729593505098</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.66584792344625</v>
       </c>
       <c r="E38">
-        <v>-31.81565103951565</v>
+        <v>-26.85242022055484</v>
       </c>
       <c r="F38">
-        <v>-2.85806235324546</v>
+        <v>-0.8179425462827816</v>
       </c>
       <c r="G38">
-        <v>-13.57814528815886</v>
+        <v>-9.290084757199093</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-16.91773506318303</v>
       </c>
       <c r="E39">
-        <v>-30.6649934589436</v>
+        <v>-26.18140247964759</v>
       </c>
       <c r="F39">
-        <v>-2.767059567108712</v>
+        <v>-1.051870187363751</v>
       </c>
       <c r="G39">
-        <v>-12.71215216968052</v>
+        <v>-9.756824537592259</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.16579722565213</v>
       </c>
       <c r="E40">
-        <v>-30.90806845815183</v>
+        <v>-25.99901835752907</v>
       </c>
       <c r="F40">
-        <v>-3.496996213270566</v>
+        <v>-0.7780434019595406</v>
       </c>
       <c r="G40">
-        <v>-12.3349139353599</v>
+        <v>-9.885008180899034</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.41117133656666</v>
       </c>
       <c r="E41">
-        <v>-31.07299455646644</v>
+        <v>-25.27749756691191</v>
       </c>
       <c r="F41">
-        <v>-3.510313047637971</v>
+        <v>-1.209057872249374</v>
       </c>
       <c r="G41">
-        <v>-14.06980723641879</v>
+        <v>-9.919556164073235</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.64471907469187</v>
       </c>
       <c r="E42">
-        <v>-30.71954381308955</v>
+        <v>-24.23001198546558</v>
       </c>
       <c r="F42">
-        <v>-3.116744097424287</v>
+        <v>-0.9367801338883986</v>
       </c>
       <c r="G42">
-        <v>-12.4192879790555</v>
+        <v>-9.94893617832933</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.87201542389056</v>
       </c>
       <c r="E43">
-        <v>-30.38986812794165</v>
+        <v>-23.9478220420001</v>
       </c>
       <c r="F43">
-        <v>-3.285023621833395</v>
+        <v>-1.041180106030623</v>
       </c>
       <c r="G43">
-        <v>-13.86592635906499</v>
+        <v>-10.18733240454995</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.08452505157094</v>
       </c>
       <c r="E44">
-        <v>-28.7900511256177</v>
+        <v>-23.87454693459615</v>
       </c>
       <c r="F44">
-        <v>-2.648288248895319</v>
+        <v>-1.226809785691367</v>
       </c>
       <c r="G44">
-        <v>-13.04850222758741</v>
+        <v>-10.58221535618961</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-18.2872116030566</v>
       </c>
       <c r="E45">
-        <v>-29.22492765362351</v>
+        <v>-23.68775625526199</v>
       </c>
       <c r="F45">
-        <v>-4.053987969810746</v>
+        <v>-1.294547044953088</v>
       </c>
       <c r="G45">
-        <v>-12.86722387153117</v>
+        <v>-10.1276795013876</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-18.47778223901522</v>
       </c>
       <c r="E46">
-        <v>-29.40255011895811</v>
+        <v>-23.0661949548108</v>
       </c>
       <c r="F46">
-        <v>-2.701789185972528</v>
+        <v>-1.289396256442481</v>
       </c>
       <c r="G46">
-        <v>-13.24690184667218</v>
+        <v>-9.991262875012753</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-18.65493588333162</v>
       </c>
       <c r="E47">
-        <v>-28.45995388952032</v>
+        <v>-23.66171977346664</v>
       </c>
       <c r="F47">
-        <v>-3.609129823485327</v>
+        <v>-1.127210202648366</v>
       </c>
       <c r="G47">
-        <v>-13.75030300798606</v>
+        <v>-9.9109002403814</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-18.82836514690917</v>
       </c>
       <c r="E48">
-        <v>-27.91292611950451</v>
+        <v>-21.68002744945867</v>
       </c>
       <c r="F48">
-        <v>-3.310136408016665</v>
+        <v>-1.15385712526162</v>
       </c>
       <c r="G48">
-        <v>-12.10302760077722</v>
+        <v>-10.71899095994574</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-18.99424289190551</v>
       </c>
       <c r="E49">
-        <v>-26.11352654696592</v>
+        <v>-21.42945590380912</v>
       </c>
       <c r="F49">
-        <v>-3.321041036507118</v>
+        <v>-1.447751939366051</v>
       </c>
       <c r="G49">
-        <v>-13.17880449012988</v>
+        <v>-9.43881234969334</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-19.16490010990399</v>
       </c>
       <c r="E50">
-        <v>-27.94594830274822</v>
+        <v>-21.83386239693032</v>
       </c>
       <c r="F50">
-        <v>-3.634895363182003</v>
+        <v>-1.285618072718312</v>
       </c>
       <c r="G50">
-        <v>-12.46311063238963</v>
+        <v>-9.776230202138002</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-19.33656176178448</v>
       </c>
       <c r="E51">
-        <v>-26.84970817355973</v>
+        <v>-20.96869448622131</v>
       </c>
       <c r="F51">
-        <v>-3.931664612174148</v>
+        <v>-1.520939856138193</v>
       </c>
       <c r="G51">
-        <v>-13.29279220972248</v>
+        <v>-10.10104337969677</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-19.51642189014397</v>
       </c>
       <c r="E52">
-        <v>-27.22819447480268</v>
+        <v>-20.81896291153859</v>
       </c>
       <c r="F52">
-        <v>-3.483498794809351</v>
+        <v>-1.445830126991557</v>
       </c>
       <c r="G52">
-        <v>-12.92312905083297</v>
+        <v>-9.630417505979734</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-19.70054477967562</v>
       </c>
       <c r="E53">
-        <v>-25.94359375239923</v>
+        <v>-19.98228603051791</v>
       </c>
       <c r="F53">
-        <v>-3.85993379366353</v>
+        <v>-1.663393370030221</v>
       </c>
       <c r="G53">
-        <v>-12.78460033208391</v>
+        <v>-10.40291463916113</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-19.88401179171965</v>
       </c>
       <c r="E54">
-        <v>-26.30714095250677</v>
+        <v>-19.69975137051248</v>
       </c>
       <c r="F54">
-        <v>-3.980910225903176</v>
+        <v>-1.489699636276415</v>
       </c>
       <c r="G54">
-        <v>-11.59977003041586</v>
+        <v>-9.729264212316171</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-20.07001703904579</v>
       </c>
       <c r="E55">
-        <v>-25.18200693213145</v>
+        <v>-19.36896470133518</v>
       </c>
       <c r="F55">
-        <v>-2.993830942196896</v>
+        <v>-1.832622203482938</v>
       </c>
       <c r="G55">
-        <v>-12.8094285131454</v>
+        <v>-10.51899095442662</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-20.24713743536874</v>
       </c>
       <c r="E56">
-        <v>-23.64866207706138</v>
+        <v>-18.64611488309408</v>
       </c>
       <c r="F56">
-        <v>-3.670098492698773</v>
+        <v>-1.479573673144594</v>
       </c>
       <c r="G56">
-        <v>-13.58155883671174</v>
+        <v>-10.1727775034545</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-20.42114686465145</v>
       </c>
       <c r="E57">
-        <v>-24.65113930738054</v>
+        <v>-18.2578394627585</v>
       </c>
       <c r="F57">
-        <v>-3.878613478596659</v>
+        <v>-1.679481093359991</v>
       </c>
       <c r="G57">
-        <v>-12.66991423831319</v>
+        <v>-9.565891648038074</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-20.582468706884</v>
       </c>
       <c r="E58">
-        <v>-24.06022040008394</v>
+        <v>-18.91148847390532</v>
       </c>
       <c r="F58">
-        <v>-3.720922146330134</v>
+        <v>-1.789168534634284</v>
       </c>
       <c r="G58">
-        <v>-12.85191185450429</v>
+        <v>-10.18447363922268</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-20.73518993141273</v>
       </c>
       <c r="E59">
-        <v>-24.03859047550423</v>
+        <v>-18.01699889124302</v>
       </c>
       <c r="F59">
-        <v>-3.447611433817868</v>
+        <v>-1.604659636069528</v>
       </c>
       <c r="G59">
-        <v>-13.28614133787661</v>
+        <v>-10.24605849338245</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-20.87541564492157</v>
       </c>
       <c r="E60">
-        <v>-22.27352965419932</v>
+        <v>-17.04692086246884</v>
       </c>
       <c r="F60">
-        <v>-3.905434358364502</v>
+        <v>-1.548222964916798</v>
       </c>
       <c r="G60">
-        <v>-13.37392109789132</v>
+        <v>-10.20995450643195</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-21.00223590370741</v>
       </c>
       <c r="E61">
-        <v>-24.25849055551993</v>
+        <v>-17.65930356589216</v>
       </c>
       <c r="F61">
-        <v>-3.521082652241768</v>
+        <v>-1.602814033496091</v>
       </c>
       <c r="G61">
-        <v>-14.5312184871015</v>
+        <v>-9.965934736362067</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-21.12292087330015</v>
       </c>
       <c r="E62">
-        <v>-23.77417627650902</v>
+        <v>-16.68090665483435</v>
       </c>
       <c r="F62">
-        <v>-3.53014084979138</v>
+        <v>-1.786055529934564</v>
       </c>
       <c r="G62">
-        <v>-12.92152605365403</v>
+        <v>-10.0779134879918</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-21.22930504794529</v>
       </c>
       <c r="E63">
-        <v>-23.87908639457419</v>
+        <v>-16.88426449414326</v>
       </c>
       <c r="F63">
-        <v>-3.7391984163381</v>
+        <v>-1.613639138715875</v>
       </c>
       <c r="G63">
-        <v>-12.83750184973364</v>
+        <v>-10.64559379188348</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-21.32902845553564</v>
       </c>
       <c r="E64">
-        <v>-24.96744788187948</v>
+        <v>-16.76491366030166</v>
       </c>
       <c r="F64">
-        <v>-4.094351828246957</v>
+        <v>-1.810127886659918</v>
       </c>
       <c r="G64">
-        <v>-13.76703396469821</v>
+        <v>-10.80773147396997</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-21.41271904289785</v>
       </c>
       <c r="E65">
-        <v>-24.41943164756836</v>
+        <v>-17.00991574956462</v>
       </c>
       <c r="F65">
-        <v>-3.419125535570399</v>
+        <v>-2.166750822341341</v>
       </c>
       <c r="G65">
-        <v>-14.39676122454228</v>
+        <v>-10.78493967368956</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-21.4830685682897</v>
       </c>
       <c r="E66">
-        <v>-22.57718754700284</v>
+        <v>-16.39407342110772</v>
       </c>
       <c r="F66">
-        <v>-4.079167025386239</v>
+        <v>-2.06638499945075</v>
       </c>
       <c r="G66">
-        <v>-14.55116196503301</v>
+        <v>-10.99129031542656</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-21.53411710211831</v>
       </c>
       <c r="E67">
-        <v>-21.82196759969601</v>
+        <v>-16.38756533896171</v>
       </c>
       <c r="F67">
-        <v>-3.556769548321773</v>
+        <v>-2.306760652395111</v>
       </c>
       <c r="G67">
-        <v>-13.69177664111477</v>
+        <v>-10.82305393397522</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-21.56223308096438</v>
       </c>
       <c r="E68">
-        <v>-23.82026446258064</v>
+        <v>-16.89088886620636</v>
       </c>
       <c r="F68">
-        <v>-4.181924344968713</v>
+        <v>-2.111352095544318</v>
       </c>
       <c r="G68">
-        <v>-13.90642945065152</v>
+        <v>-10.77934745877539</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-21.57243022945564</v>
       </c>
       <c r="E69">
-        <v>-23.78882880606302</v>
+        <v>-16.06876068445655</v>
       </c>
       <c r="F69">
-        <v>-4.462786454724899</v>
+        <v>-1.996927221093414</v>
       </c>
       <c r="G69">
-        <v>-14.51592605065905</v>
+        <v>-10.5226995171183</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-21.55670883480066</v>
       </c>
       <c r="E70">
-        <v>-21.61245470120371</v>
+        <v>-16.34037239867769</v>
       </c>
       <c r="F70">
-        <v>-4.216193076055125</v>
+        <v>-2.140978655705443</v>
       </c>
       <c r="G70">
-        <v>-13.74169538306916</v>
+        <v>-10.70382775536055</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-21.52570987195936</v>
       </c>
       <c r="E71">
-        <v>-21.87933175451455</v>
+        <v>-16.58829004229068</v>
       </c>
       <c r="F71">
-        <v>-4.28773088496089</v>
+        <v>-2.26469284221134</v>
       </c>
       <c r="G71">
-        <v>-14.62012478340727</v>
+        <v>-10.20229719254621</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.47509643704329</v>
       </c>
       <c r="E72">
-        <v>-22.82958235242399</v>
+        <v>-16.77375584721222</v>
       </c>
       <c r="F72">
-        <v>-4.046908741986421</v>
+        <v>-2.107172153629792</v>
       </c>
       <c r="G72">
-        <v>-13.45501604638048</v>
+        <v>-10.35978644388824</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.4128870993585</v>
       </c>
       <c r="E73">
-        <v>-23.4742645803205</v>
+        <v>-15.4687503975699</v>
       </c>
       <c r="F73">
-        <v>-4.390030945737018</v>
+        <v>-2.269576068050843</v>
       </c>
       <c r="G73">
-        <v>-13.33044045209863</v>
+        <v>-10.98318003735427</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.33969915412018</v>
       </c>
       <c r="E74">
-        <v>-23.90416763776483</v>
+        <v>-17.21097270979957</v>
       </c>
       <c r="F74">
-        <v>-4.333449310288798</v>
+        <v>-2.429927288047758</v>
       </c>
       <c r="G74">
-        <v>-13.11417420240458</v>
+        <v>-10.4059796533111</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-21.25615714804396</v>
       </c>
       <c r="E75">
-        <v>-23.97310679254566</v>
+        <v>-16.73118543113273</v>
       </c>
       <c r="F75">
-        <v>-4.621165331935748</v>
+        <v>-2.457941016875631</v>
       </c>
       <c r="G75">
-        <v>-13.46739880797613</v>
+        <v>-10.49415233038677</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-21.16893689727624</v>
       </c>
       <c r="E76">
-        <v>-23.50300064947699</v>
+        <v>-16.62625039379961</v>
       </c>
       <c r="F76">
-        <v>-4.442113717820634</v>
+        <v>-2.293552334157472</v>
       </c>
       <c r="G76">
-        <v>-14.16508374952688</v>
+        <v>-10.32365112800264</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-21.0688034814671</v>
       </c>
       <c r="E77">
-        <v>-23.54611513624004</v>
+        <v>-17.04369797048077</v>
       </c>
       <c r="F77">
-        <v>-4.375929647439162</v>
+        <v>-3.027181013833604</v>
       </c>
       <c r="G77">
-        <v>-14.63663382682917</v>
+        <v>-10.35169835714497</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.96135854213719</v>
       </c>
       <c r="E78">
-        <v>-23.04014186017015</v>
+        <v>-16.95411320220423</v>
       </c>
       <c r="F78">
-        <v>-4.897560056288636</v>
+        <v>-2.352938821631572</v>
       </c>
       <c r="G78">
-        <v>-12.94967771258</v>
+        <v>-10.31178137771914</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.83434806854513</v>
       </c>
       <c r="E79">
-        <v>-24.73631751844145</v>
+        <v>-16.69555918438835</v>
       </c>
       <c r="F79">
-        <v>-4.475045463918929</v>
+        <v>-2.93797247149132</v>
       </c>
       <c r="G79">
-        <v>-13.78502982716475</v>
+        <v>-10.42975831504696</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-20.68718760067836</v>
       </c>
       <c r="E80">
-        <v>-23.60119502482991</v>
+        <v>-17.08758080133892</v>
       </c>
       <c r="F80">
-        <v>-4.38652198141876</v>
+        <v>-2.76733127161683</v>
       </c>
       <c r="G80">
-        <v>-13.59089485936956</v>
+        <v>-10.03362742749275</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-20.51375165603696</v>
       </c>
       <c r="E81">
-        <v>-25.68805496600518</v>
+        <v>-17.87419071983879</v>
       </c>
       <c r="F81">
-        <v>-4.799172374755931</v>
+        <v>-2.870579813069163</v>
       </c>
       <c r="G81">
-        <v>-12.70216085013033</v>
+        <v>-9.612405979045644</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-20.30904259480659</v>
       </c>
       <c r="E82">
-        <v>-25.34482112248738</v>
+        <v>-19.0144092037459</v>
       </c>
       <c r="F82">
-        <v>-5.049011296909873</v>
+        <v>-2.601203845720195</v>
       </c>
       <c r="G82">
-        <v>-12.89447351820091</v>
+        <v>-9.640680342967402</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-20.07804617784384</v>
       </c>
       <c r="E83">
-        <v>-26.02999716080097</v>
+        <v>-19.95654857993795</v>
       </c>
       <c r="F83">
-        <v>-4.573202859313656</v>
+        <v>-2.880177277797999</v>
       </c>
       <c r="G83">
-        <v>-12.90398185000175</v>
+        <v>-9.824261375753009</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-19.81562154420673</v>
       </c>
       <c r="E84">
-        <v>-27.11866183253297</v>
+        <v>-19.84951201767447</v>
       </c>
       <c r="F84">
-        <v>-4.530533654395454</v>
+        <v>-3.01988889558676</v>
       </c>
       <c r="G84">
-        <v>-13.9319938616877</v>
+        <v>-9.925703162213011</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-19.53586004814627</v>
       </c>
       <c r="E85">
-        <v>-27.03328426732847</v>
+        <v>-20.77515899169563</v>
       </c>
       <c r="F85">
-        <v>-4.587514562931823</v>
+        <v>-3.002788078923367</v>
       </c>
       <c r="G85">
-        <v>-12.28602382677442</v>
+        <v>-9.87699188963202</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-19.23958255313914</v>
       </c>
       <c r="E86">
-        <v>-27.69288067709244</v>
+        <v>-21.11723824246513</v>
       </c>
       <c r="F86">
-        <v>-5.436847116328781</v>
+        <v>-3.049317475938615</v>
       </c>
       <c r="G86">
-        <v>-13.4792489776752</v>
+        <v>-10.05210627770865</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.94044950691113</v>
       </c>
       <c r="E87">
-        <v>-29.15410917071819</v>
+        <v>-23.08968551806403</v>
       </c>
       <c r="F87">
-        <v>-4.752027500760402</v>
+        <v>-3.050775402567543</v>
       </c>
       <c r="G87">
-        <v>-13.04893430581724</v>
+        <v>-9.123474869628017</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.65098510413461</v>
       </c>
       <c r="E88">
-        <v>-29.37895987863309</v>
+        <v>-22.84950530714919</v>
       </c>
       <c r="F88">
-        <v>-5.198105832270144</v>
+        <v>-2.968574020085539</v>
       </c>
       <c r="G88">
-        <v>-13.29784269513399</v>
+        <v>-9.607292835763948</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-18.38020849687292</v>
       </c>
       <c r="E89">
-        <v>-30.18838546354591</v>
+        <v>-25.68823770730348</v>
       </c>
       <c r="F89">
-        <v>-5.055581907148878</v>
+        <v>-3.476655651694824</v>
       </c>
       <c r="G89">
-        <v>-12.06094500871306</v>
+        <v>-9.650772176184349</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.14648877405599</v>
       </c>
       <c r="E90">
-        <v>-32.82075517599777</v>
+        <v>-25.36228952931961</v>
       </c>
       <c r="F90">
-        <v>-5.27137492904776</v>
+        <v>-3.19586809500489</v>
       </c>
       <c r="G90">
-        <v>-13.06040852829519</v>
+        <v>-9.565173693275518</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.95189854878565</v>
       </c>
       <c r="E91">
-        <v>-33.5934559897708</v>
+        <v>-27.73159691306249</v>
       </c>
       <c r="F91">
-        <v>-5.201440839433815</v>
+        <v>-3.600144522267161</v>
       </c>
       <c r="G91">
-        <v>-13.75938448304624</v>
+        <v>-9.272172438559465</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.81225424432565</v>
       </c>
       <c r="E92">
-        <v>-34.86442587260616</v>
+        <v>-29.4522702883333</v>
       </c>
       <c r="F92">
-        <v>-5.24654875798586</v>
+        <v>-3.598131589478358</v>
       </c>
       <c r="G92">
-        <v>-12.4358857877935</v>
+        <v>-9.703393038790534</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.7275777122516</v>
       </c>
       <c r="E93">
-        <v>-36.01265174794752</v>
+        <v>-30.94694043954657</v>
       </c>
       <c r="F93">
-        <v>-5.27050182980521</v>
+        <v>-3.764831417250328</v>
       </c>
       <c r="G93">
-        <v>-13.7771701805732</v>
+        <v>-9.647328604068671</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.70207074822488</v>
       </c>
       <c r="E94">
-        <v>-36.48228442492516</v>
+        <v>-31.99514244994643</v>
       </c>
       <c r="F94">
-        <v>-4.886715070251185</v>
+        <v>-3.57861773857061</v>
       </c>
       <c r="G94">
-        <v>-14.08066662854553</v>
+        <v>-9.773934052270119</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.73851125433098</v>
       </c>
       <c r="E95">
-        <v>-36.91957604531636</v>
+        <v>-33.98582232326132</v>
       </c>
       <c r="F95">
-        <v>-5.400245702636085</v>
+        <v>-3.989809376911451</v>
       </c>
       <c r="G95">
-        <v>-13.40011861449085</v>
+        <v>-9.850781319309538</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.82589267883167</v>
       </c>
       <c r="E96">
-        <v>-40.42535156314003</v>
+        <v>-35.53390900192888</v>
       </c>
       <c r="F96">
-        <v>-4.831245932224924</v>
+        <v>-4.054846158440045</v>
       </c>
       <c r="G96">
-        <v>-13.55450891200322</v>
+        <v>-10.33954142495645</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.95865381846138</v>
       </c>
       <c r="E97">
-        <v>-42.2952290552553</v>
+        <v>-38.0504498037426</v>
       </c>
       <c r="F97">
-        <v>-5.710465981514889</v>
+        <v>-4.115252366186991</v>
       </c>
       <c r="G97">
-        <v>-13.46965449130285</v>
+        <v>-9.730382916373463</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.11462861556014</v>
       </c>
       <c r="E98">
-        <v>-42.82132256358832</v>
+        <v>-40.2517805554528</v>
       </c>
       <c r="F98">
-        <v>-4.782178417487499</v>
+        <v>-4.351159805360651</v>
       </c>
       <c r="G98">
-        <v>-14.52051835039482</v>
+        <v>-10.46785168937589</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.27849886415736</v>
       </c>
       <c r="E99">
-        <v>-46.00383599285245</v>
+        <v>-42.23073175998637</v>
       </c>
       <c r="F99">
-        <v>-5.127709513645437</v>
+        <v>-4.26339013719703</v>
       </c>
       <c r="G99">
-        <v>-14.52444491025985</v>
+        <v>-10.87339561655336</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.4306166849739</v>
       </c>
       <c r="E100">
-        <v>-46.7872842792313</v>
+        <v>-43.92139818343529</v>
       </c>
       <c r="F100">
-        <v>-5.062548477006422</v>
+        <v>-4.519320044863757</v>
       </c>
       <c r="G100">
-        <v>-14.08936824026771</v>
+        <v>-11.8604881228905</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.54656871046454</v>
       </c>
       <c r="E101">
-        <v>-47.74540417429846</v>
+        <v>-45.13299791038222</v>
       </c>
       <c r="F101">
-        <v>-5.092286038399521</v>
+        <v>-4.76694308421521</v>
       </c>
       <c r="G101">
-        <v>-15.10257341400516</v>
+        <v>-11.4583603550105</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.63113338904853</v>
       </c>
       <c r="E102">
-        <v>-50.46531216014657</v>
+        <v>-47.48540276233589</v>
       </c>
       <c r="F102">
-        <v>-5.58876058596078</v>
+        <v>-4.741218134521271</v>
       </c>
       <c r="G102">
-        <v>-14.86527239514051</v>
+        <v>-11.4003091436548</v>
       </c>
     </row>
   </sheetData>
